--- a/Lab03/Data/Measurements.xlsx
+++ b/Lab03/Data/Measurements.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/g_tec/Git/EEK_lab/Lab03/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21555E0-1B8B-C841-85A7-46C2F79E56F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5219351-CD06-4947-9479-E81423974137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20640" yWindow="1040" windowWidth="20340" windowHeight="23840" xr2:uid="{D9E6CFC8-537B-4848-AA3D-903F2328991C}"/>
+    <workbookView xWindow="18680" yWindow="800" windowWidth="22440" windowHeight="24140" xr2:uid="{D9E6CFC8-537B-4848-AA3D-903F2328991C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="115">
   <si>
     <t>ohm</t>
   </si>
@@ -143,9 +143,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>ohm?</t>
-  </si>
-  <si>
     <t>a. Calculating voltage gain</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t>Vrms</t>
   </si>
   <si>
-    <t>Also getting multimeter value of 2.083</t>
-  </si>
-  <si>
     <t>Vsig meas</t>
   </si>
   <si>
@@ -375,16 +369,27 @@
   </si>
   <si>
     <t>IE calc = IC</t>
+  </si>
+  <si>
+    <t>Also getting multimeter value of 2.083 but I will use scope value</t>
+  </si>
+  <si>
+    <t>Pi</t>
+  </si>
+  <si>
+    <t>Po</t>
+  </si>
+  <si>
+    <t>difference in %</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -415,11 +420,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -755,11 +759,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA974360-84BA-024E-B190-05E1380E7925}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -818,7 +822,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -863,7 +867,7 @@
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" t="s">
@@ -874,7 +878,7 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>B13*(B5/(B6+B5))</f>
         <v>2.2871364583549676</v>
       </c>
@@ -889,7 +893,7 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>B14-0.7</f>
         <v>1.5871364583549676</v>
       </c>
@@ -919,7 +923,7 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>B13-(B16*B4)</f>
         <v>5.2282545995074772</v>
       </c>
@@ -927,19 +931,19 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>25/(B16*1000)</f>
         <v>15.72171054898627</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -1013,12 +1017,12 @@
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <f>25/(B25*1000)</f>
         <v>16.192407527579494</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -1028,7 +1032,7 @@
       <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <f>100*((B26-B18)/B18)</f>
         <v>2.9939298088882245</v>
       </c>
@@ -1041,98 +1045,98 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3">
+        <v>36</v>
+      </c>
+      <c r="B31" s="2">
         <f>-B4/B26</f>
         <v>-185.32142270313597</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B34">
         <v>14</v>
       </c>
       <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
         <v>41</v>
-      </c>
-      <c r="D34" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>2.14</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37">
         <v>13.7</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38">
         <f>- B36/(B37/1000)</f>
         <v>-156.20437956204381</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="3">
+        <v>56</v>
+      </c>
+      <c r="B39" s="2">
         <f>100*((B38-B31)/B31)</f>
         <v>-15.711644512752516</v>
       </c>
@@ -1140,35 +1144,35 @@
         <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>250</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" s="3">
+        <v>54</v>
+      </c>
+      <c r="B44" s="2">
         <f>1/((1/B6)+(1/B5)+(1/(B43*B26)))</f>
         <v>2646.5819581989003</v>
       </c>
@@ -1176,17 +1180,17 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>986.3</v>
@@ -1197,43 +1201,43 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B49">
         <v>19.7</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <f>(B50/(B49-B50))*B47</f>
@@ -1243,14 +1247,14 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="3">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2">
         <f>100*((B51-B44)/B44)</f>
         <v>-8.4671751590578754</v>
       </c>
@@ -1258,22 +1262,22 @@
         <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56">
         <f>B4</f>
@@ -1283,42 +1287,42 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B59">
         <v>14</v>
       </c>
       <c r="C59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D59" t="s">
         <v>41</v>
-      </c>
-      <c r="D59" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B60">
         <v>13.7</v>
       </c>
       <c r="C60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61">
         <v>2.14</v>
@@ -1329,7 +1333,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B62">
         <v>3001</v>
@@ -1340,7 +1344,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>1.08</v>
@@ -1351,9 +1355,9 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="3">
+        <v>69</v>
+      </c>
+      <c r="B64" s="2">
         <f>((B61-B63)/B63)*B62</f>
         <v>2945.4259259259261</v>
       </c>
@@ -1361,14 +1365,14 @@
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" s="3">
+        <v>72</v>
+      </c>
+      <c r="B65" s="2">
         <f>100*((B64-B56)/B56)</f>
         <v>-1.8453103863661051</v>
       </c>
@@ -1376,22 +1380,22 @@
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B69">
         <v>986.6</v>
@@ -1402,7 +1406,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B70">
         <v>176.2</v>
@@ -1413,7 +1417,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B71">
         <v>134.02000000000001</v>
@@ -1424,7 +1428,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>20.07</v>
@@ -1435,45 +1439,45 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B74">
         <v>8.15</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B75">
         <v>8.11</v>
       </c>
       <c r="C75" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B76">
         <v>87.3</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -1491,7 +1495,7 @@
       <c r="A79" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="2">
         <f>B78*(B70/(B70+B69))</f>
         <v>1.5153078775369797</v>
       </c>
@@ -1506,7 +1510,7 @@
       <c r="A80" t="s">
         <v>12</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="2">
         <f>B79-0.7</f>
         <v>0.81530787753697975</v>
       </c>
@@ -1519,7 +1523,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B81" s="1">
         <f>B80/B72</f>
@@ -1536,7 +1540,7 @@
       <c r="A82" t="s">
         <v>17</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="2">
         <f>B78-(B81*B71)</f>
         <v>4.5556770429742883</v>
       </c>
@@ -1544,12 +1548,12 @@
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -1589,7 +1593,7 @@
       <c r="A88" t="s">
         <v>25</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="3">
         <v>4.5999999999999996</v>
       </c>
       <c r="C88" t="s">
@@ -1613,84 +1617,84 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>102</v>
-      </c>
-      <c r="B93" s="2">
+        <v>100</v>
+      </c>
+      <c r="B93" s="1">
         <f>B78*B81</f>
         <v>0.40623212632634764</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B98">
         <f>2*B88</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="C98" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1">
         <f>(9^2)/(8*B71)</f>
         <v>7.5548425608118183E-2</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B101">
         <f>(B100/B93)*100</f>
@@ -1702,57 +1706,57 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B104">
         <v>40</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B105">
         <v>23</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B106">
         <v>2.38</v>
       </c>
       <c r="C106" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>104</v>
-      </c>
-      <c r="B107" s="4">
+        <v>102</v>
+      </c>
+      <c r="B107" s="3">
         <f>B85-B88</f>
         <v>5.370000000000001</v>
       </c>
       <c r="D107" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B108" s="1">
         <f>(B85-B88)/B71</f>
@@ -1762,41 +1766,41 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B109" s="1">
         <f>B85*B108</f>
         <v>0.39948440531264001</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D109" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B110" s="1">
         <f>(B106^2)/B71</f>
         <v>4.2265333532308602E-2</v>
       </c>
       <c r="C110" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>108</v>
-      </c>
-      <c r="B111" s="3">
+        <v>106</v>
+      </c>
+      <c r="B111" s="2">
         <f>(B110/B109)*100</f>
         <v>10.579970824951571</v>
       </c>
@@ -1804,7 +1808,40 @@
         <v>34</v>
       </c>
     </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2">
+        <f>100*((B109-B93)/B93)</f>
+        <v>-1.6610505610988608</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2">
+        <f>100*((B110-B100)/B100)</f>
+        <v>-44.055308641975316</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>106</v>
+      </c>
+      <c r="B116" s="2">
+        <f>100*((B111-B101)/B101)</f>
+        <v>-43.110342669682865</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>